--- a/backend/excel-templates/test-data/master_external_users_test_data.xlsx
+++ b/backend/excel-templates/test-data/master_external_users_test_data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Externals" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E11"/>
+  <cols>
+    <col min="1" max="1" width="30.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="20.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,58 +425,177 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>umesh.lama@ioe.edu.np</v>
+        <v>external1@pcampus.edu.np</v>
       </c>
       <c r="B2" t="str">
-        <v>pass123</v>
+        <v>subesh</v>
       </c>
       <c r="C2" t="str">
-        <v>Umesh</v>
+        <v>External</v>
       </c>
       <c r="D2" t="str">
-        <v>Lama</v>
+        <v>1</v>
       </c>
       <c r="E2" t="str">
-        <v>Dr.</v>
+        <v>Professor</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>sunita.acharya@ioe.edu.np</v>
+        <v>external2@pcampus.edu.np</v>
       </c>
       <c r="B3" t="str">
-        <v>pass123</v>
+        <v>subesh</v>
       </c>
       <c r="C3" t="str">
-        <v>Sunita</v>
+        <v>External</v>
       </c>
       <c r="D3" t="str">
-        <v>Acharya</v>
+        <v>2</v>
       </c>
       <c r="E3" t="str">
-        <v>Prof.</v>
+        <v>Professor</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>roshan.karki@ioe.edu.np</v>
+        <v>external3@pcampus.edu.np</v>
       </c>
       <c r="B4" t="str">
-        <v>pass123</v>
+        <v>subesh</v>
       </c>
       <c r="C4" t="str">
-        <v>Roshan</v>
+        <v>External</v>
       </c>
       <c r="D4" t="str">
-        <v>Karki</v>
+        <v>3</v>
       </c>
       <c r="E4" t="str">
-        <v>Dr.</v>
+        <v>Professor</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>external4@pcampus.edu.np</v>
+      </c>
+      <c r="B5" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C5" t="str">
+        <v>External</v>
+      </c>
+      <c r="D5" t="str">
+        <v>4</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Professor</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>external5@pcampus.edu.np</v>
+      </c>
+      <c r="B6" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C6" t="str">
+        <v>External</v>
+      </c>
+      <c r="D6" t="str">
+        <v>5</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Professor</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>external6@pcampus.edu.np</v>
+      </c>
+      <c r="B7" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C7" t="str">
+        <v>External</v>
+      </c>
+      <c r="D7" t="str">
+        <v>6</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Professor</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>external7@pcampus.edu.np</v>
+      </c>
+      <c r="B8" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C8" t="str">
+        <v>External</v>
+      </c>
+      <c r="D8" t="str">
+        <v>7</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Professor</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>external8@pcampus.edu.np</v>
+      </c>
+      <c r="B9" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C9" t="str">
+        <v>External</v>
+      </c>
+      <c r="D9" t="str">
+        <v>8</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Professor</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>external9@pcampus.edu.np</v>
+      </c>
+      <c r="B10" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C10" t="str">
+        <v>External</v>
+      </c>
+      <c r="D10" t="str">
+        <v>9</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Professor</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>external10@pcampus.edu.np</v>
+      </c>
+      <c r="B11" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C11" t="str">
+        <v>External</v>
+      </c>
+      <c r="D11" t="str">
+        <v>10</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Professor</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E11"/>
   </ignoredErrors>
 </worksheet>
 </file>